--- a/data/trans_orig/IP04D$aparatos-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36851</t>
+          <t>36989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52023</t>
+          <t>52148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>33944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>48556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>73980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96802</t>
+          <t>97247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>37785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53082</t>
+          <t>52944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>55819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82895</t>
+          <t>82450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105475</t>
+          <t>105717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44182</t>
+          <t>44319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60247</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>39413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55078</t>
+          <t>55185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89592</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111926</t>
+          <t>110682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32228</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>41593</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57327</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77328</t>
+          <t>78572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99662</t>
+          <t>101182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>48496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63120</t>
+          <t>63830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49873</t>
+          <t>49764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64365</t>
+          <t>64425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102797</t>
+          <t>103826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124850</t>
+          <t>123452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37192</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37017</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48197</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70250</t>
+          <t>69221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131968</t>
+          <t>131702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153567</t>
+          <t>152882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129008</t>
+          <t>129051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153427</t>
+          <t>153498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>267124</t>
+          <t>268259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301052</t>
+          <t>301564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>53226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>74406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74051</t>
+          <t>73980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98470</t>
+          <t>98427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132533</t>
+          <t>132021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166461</t>
+          <t>165326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89334</t>
+          <t>89678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107750</t>
+          <t>107596</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>84225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103333</t>
+          <t>103924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180372</t>
+          <t>179382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206059</t>
+          <t>207556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58220</t>
+          <t>57876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56170</t>
+          <t>56178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81899</t>
+          <t>80402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107586</t>
+          <t>108576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44092</t>
+          <t>43802</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46668</t>
+          <t>46972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59296</t>
+          <t>59598</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84663</t>
+          <t>84885</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100831</t>
+          <t>101071</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42593</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>414087</t>
+          <t>416347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>454984</t>
+          <t>454272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>413043</t>
+          <t>414658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>458247</t>
+          <t>456071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>840833</t>
+          <t>841834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>900626</t>
+          <t>899829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>220461</t>
+          <t>221173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>261358</t>
+          <t>259098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>257104</t>
+          <t>259280</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302308</t>
+          <t>300693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>490170</t>
+          <t>490967</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>549963</t>
+          <t>548962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42919</t>
+          <t>44120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34895</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51326</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68750</t>
+          <t>68983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90912</t>
+          <t>90205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>38970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54547</t>
+          <t>54352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47712</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64143</t>
+          <t>63835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91216</t>
+          <t>91923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113378</t>
+          <t>113145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45621</t>
+          <t>45579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63566</t>
+          <t>62450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>40089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56945</t>
+          <t>56939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90054</t>
+          <t>90691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114992</t>
+          <t>114091</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40855</t>
+          <t>41971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58800</t>
+          <t>58842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55131</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72206</t>
+          <t>71987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101505</t>
+          <t>102406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126443</t>
+          <t>125806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>27345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>39423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29974</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>44169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>60796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79946</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34243</t>
+          <t>34495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30893</t>
+          <t>30613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44808</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>56217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75197</t>
+          <t>75826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100659</t>
+          <t>101247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124607</t>
+          <t>125747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106189</t>
+          <t>106021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129868</t>
+          <t>130248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214268</t>
+          <t>215222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248049</t>
+          <t>248021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98970</t>
+          <t>97830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122918</t>
+          <t>122330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78894</t>
+          <t>78514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102573</t>
+          <t>102741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184290</t>
+          <t>184318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218071</t>
+          <t>217117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78192</t>
+          <t>79006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96163</t>
+          <t>97211</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78377</t>
+          <t>77542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98314</t>
+          <t>97495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161588</t>
+          <t>162990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>188232</t>
+          <t>189096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39368</t>
+          <t>38320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57339</t>
+          <t>56525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44109</t>
+          <t>44928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64046</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89722</t>
+          <t>88858</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116366</t>
+          <t>114964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>24543</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>37013</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44617</t>
+          <t>44610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>59408</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78164</t>
+          <t>77940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23587</t>
+          <t>24074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36411</t>
+          <t>36544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>23215</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50748</t>
+          <t>50972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69830</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>332827</t>
+          <t>334324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>374490</t>
+          <t>376590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>350049</t>
+          <t>352865</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>394476</t>
+          <t>397513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>695846</t>
+          <t>695222</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>757728</t>
+          <t>758317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>295056</t>
+          <t>292956</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>336719</t>
+          <t>335222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310428</t>
+          <t>307391</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>354855</t>
+          <t>352039</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616723</t>
+          <t>616134</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>678605</t>
+          <t>679229</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59673</t>
+          <t>59317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46417</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68896</t>
+          <t>70181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>94160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123197</t>
+          <t>122679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61337</t>
+          <t>62380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66362</t>
+          <t>65077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88841</t>
+          <t>89294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116522</t>
+          <t>117040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146170</t>
+          <t>145559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45813</t>
+          <t>45655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61564</t>
+          <t>61818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>45402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62541</t>
+          <t>62105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95935</t>
+          <t>96840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119011</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33117</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33032</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50200</t>
+          <t>50171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71243</t>
+          <t>70970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94319</t>
+          <t>93414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37774</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>34013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48313</t>
+          <t>48389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65621</t>
+          <t>65676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>83843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15540</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>31871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50093</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121810</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168814</t>
+          <t>170999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117160</t>
+          <t>117105</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145503</t>
+          <t>146985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249934</t>
+          <t>252328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305802</t>
+          <t>306527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49012</t>
+          <t>46827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96016</t>
+          <t>93969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72769</t>
+          <t>71287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101112</t>
+          <t>101167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130295</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>186163</t>
+          <t>183769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73966</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91447</t>
+          <t>90932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82540</t>
+          <t>81959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117742</t>
+          <t>118535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160349</t>
+          <t>163290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203510</t>
+          <t>204236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45462</t>
+          <t>45087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44875</t>
+          <t>44082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80077</t>
+          <t>80658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78535</t>
+          <t>77809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121696</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54491</t>
+          <t>54912</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42490</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>56704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86333</t>
+          <t>86817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>106875</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28423</t>
+          <t>28378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>34023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54565</t>
+          <t>54081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>383534</t>
+          <t>383252</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>440750</t>
+          <t>442254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>409663</t>
+          <t>412248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>466622</t>
+          <t>469504</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>815047</t>
+          <t>813924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>900452</t>
+          <t>893701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216403</t>
+          <t>214899</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273619</t>
+          <t>273901</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>280953</t>
+          <t>278071</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>337912</t>
+          <t>335327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>504276</t>
+          <t>511027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>589681</t>
+          <t>590804</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$aparatos-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41230</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33049</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48086</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>44218</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36989</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52148</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36305</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51239</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41230</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33944</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48556</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73980</t>
+          <t>75015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97247</t>
+          <t>96938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48533</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41677</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56714</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>54,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>46,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>45715</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>37785</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52944</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>38694</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53628</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,83%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>48533</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>41207</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55819</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>54,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82450</t>
+          <t>82759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105717</t>
+          <t>104682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>89933</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47345</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38944</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56111</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>52712</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44319</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60177</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44943</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>60069</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>57,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>47,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>47345</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39413</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>55185</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>88884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110682</t>
+          <t>110161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49433</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40667</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>57834</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>39763</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32298</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>48156</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32406</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47532</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>43,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49433</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>41593</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>57365</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78572</t>
+          <t>79093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101182</t>
+          <t>100370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,102 +1413,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>57262</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49728</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>63585</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>56780</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48496</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63830</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>48668</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>63644</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>65,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57262</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>49764</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>64425</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>56,49%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>73,87%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>114043</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>103024</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>123495</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>65,9%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>57,27%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>74,15%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>114043</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>103826</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>123452</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>65,9%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -1521,107 +1521,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29628</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23305</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37162</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>29377</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22327</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37661</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22513</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>37489</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29628</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22465</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37126</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>26,13%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>43,51%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>59004</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>49552</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>70023</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>42,73%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>59004</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>49595</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>69221</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>34,1%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>141873</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>127581</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>153053</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>56,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>143013</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>152882</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>130435</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>153411</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>69,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>63,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>141873</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>129051</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>153498</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>62,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268259</t>
+          <t>269377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301564</t>
+          <t>301388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85605</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74425</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99897</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>63095</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>53226</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>74406</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>52697</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>75673</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>30,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>85605</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>73980</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>98427</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>37,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132021</t>
+          <t>132197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165326</t>
+          <t>164208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206108</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94798</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>85407</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>104154</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>67,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>99305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>89678</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>89478</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>108210</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>67,3%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>60,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>72,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>94798</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>84225</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>103924</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179382</t>
+          <t>180124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207556</t>
+          <t>207039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45605</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36249</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>54996</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>48249</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39958</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>57876</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>39344</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>58076</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>45605</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36479</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>56178</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>80919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108576</t>
+          <t>107834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>140403</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147554</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>140403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>53768</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>47044</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>59503</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>63,54%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>80,37%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>39143</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>33082</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>43802</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>32870</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>44225</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>73,55%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>62,17%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>82,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>53768</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>46972</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>59598</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>72,62%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84885</t>
+          <t>84075</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101071</t>
+          <t>100570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20270</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14535</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>26994</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,63%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>36,46%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>14074</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>9415</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20135</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>8992</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>20347</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>26,45%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>37,83%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>20270</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>14440</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>27066</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42371</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>436278</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>415338</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>458761</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,06%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,13%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>435172</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>416347</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>454272</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>413256</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>453726</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>64,43%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>61,64%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,26%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>436278</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>414658</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>456071</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>60,99%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>841834</t>
+          <t>840121</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>899829</t>
+          <t>899796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>279073</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>256590</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>300013</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>39,01%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35,87%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,94%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>344</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>240273</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>221173</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>259098</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>221719</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>262189</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>35,57%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>38,36%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>279073</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>259280</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>300693</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>39,01%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>490967</t>
+          <t>491000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>548962</t>
+          <t>550675</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>715351</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>976</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>675445</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>715351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43512</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34875</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51424</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35999</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28738</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44120</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29200</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43587</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43512</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>35203</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51712</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>67929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>90065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55526</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47614</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64163</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47091</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>38970</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54352</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39503</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53890</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>56,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55526</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47326</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63835</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91923</t>
+          <t>92063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113145</t>
+          <t>114199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99038</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>48154</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39890</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56859</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>54080</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45579</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>62450</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>46161</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>62817</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>51,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>43,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>59,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>48154</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>40089</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>56939</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>42,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90691</t>
+          <t>89486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114091</t>
+          <t>113962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63922</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55217</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72186</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>57,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>50341</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41971</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58842</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>41604</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>58260</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>48,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>56,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>63922</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>55137</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>71987</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>57,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102406</t>
+          <t>102535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125806</t>
+          <t>127011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104421</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36984</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30041</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44937</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33446</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27345</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39423</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27200</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>40346</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>36984</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>29614</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>44169</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60796</t>
+          <t>60832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80405</t>
+          <t>79906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37798</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29845</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44741</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>28394</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22417</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34495</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21494</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34640</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>45,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37798</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30613</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>45168</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>56716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75826</t>
+          <t>75790</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74782</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>118242</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105795</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>131184</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>50,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>112828</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>101247</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125747</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>101365</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>125761</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>50,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>45,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>118242</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>106021</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>130248</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>56,64%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215222</t>
+          <t>213124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248021</t>
+          <t>247038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>90520</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77578</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>102967</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>49,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>110749</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97830</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>122330</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97816</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>122212</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>49,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>54,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>90520</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78514</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102741</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184318</t>
+          <t>185301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217117</t>
+          <t>219215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208762</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88368</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>78494</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>97809</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,11%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>87764</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>79006</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>97211</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>78885</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>96518</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>88368</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>77542</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>97495</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,05%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162990</t>
+          <t>162184</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189096</t>
+          <t>189232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>54055</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44614</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>63929</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>47767</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38320</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>56525</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>39013</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>56646</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>54055</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>44928</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>64881</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,95%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88858</t>
+          <t>88722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>114964</t>
+          <t>115770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>142423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135531</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>142423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>38015</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>31729</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>44353</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>56,05%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>46,78%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>30574</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>24543</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>37013</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>24038</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>37069</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>50,05%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>40,18%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>60,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>38015</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>31298</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>44610</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>56,05%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59408</t>
+          <t>58956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>77722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29810</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>36096</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>43,95%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>34,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>53,22%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>30513</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>24074</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>36544</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>24018</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>37049</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>49,95%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>59,82%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>29810</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>23215</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>36527</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50972</t>
+          <t>51190</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69504</t>
+          <t>69956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>373275</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>353121</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>396872</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>52,95%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>50,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>56,3%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>354691</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>334324</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>376590</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>333343</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>374832</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>52,97%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>373275</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>352865</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>397513</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>52,95%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>695222</t>
+          <t>695989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>758317</t>
+          <t>760820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>331629</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>308032</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>351783</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>47,05%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>49,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>482</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>314855</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>292956</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>335222</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>294714</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>336203</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>47,03%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,75%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>50,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>331629</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>307391</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>352039</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616134</t>
+          <t>613631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>679229</t>
+          <t>678462</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -5646,52 +5646,52 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>704904</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>669546</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>704904</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56887</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46738</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66147</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50791</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42082</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59317</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>58269</t>
+          <t>49241</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45964</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70181</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>109059</t>
+          <t>106128</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>92546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122679</t>
+          <t>118555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64114</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54854</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74263</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53671</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45145</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>62380</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51,38%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76989</t>
+          <t>53686</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65077</t>
+          <t>45141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89294</t>
+          <t>62534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>130660</t>
+          <t>117800</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117040</t>
+          <t>105373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145559</t>
+          <t>131382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135258</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239719</t>
+          <t>223928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>52449</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43946</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60023</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>57,39%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>65,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53919</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45655</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>61818</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54173</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45402</t>
+          <t>47260</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62105</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>108092</t>
+          <t>108247</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96840</t>
+          <t>96235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119284</t>
+          <t>119689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38949</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31375</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47452</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>40762</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32863</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49026</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>43,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>51,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41400</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50171</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>82162</t>
+          <t>79697</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70970</t>
+          <t>68255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93414</t>
+          <t>91709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38414</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32299</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44286</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>67,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32747</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26614</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38465</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>39919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74541</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65676</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83843</t>
+          <t>81365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18527</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12655</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19114</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13396</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25247</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>36,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>41173</t>
+          <t>37508</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31871</t>
+          <t>29058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50038</t>
+          <t>45203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>122620</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>108346</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>136105</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>60,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>53,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>141168</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>123857</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>170999</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>64,81%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>56,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>132722</t>
+          <t>113346</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117105</t>
+          <t>102030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146985</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>273889</t>
+          <t>235967</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252328</t>
+          <t>219336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>306527</t>
+          <t>252240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79324</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>65839</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>93598</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>46,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>76658</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>46827</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93969</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>35,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>85550</t>
+          <t>65237</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71287</t>
+          <t>55130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101167</t>
+          <t>76553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>162208</t>
+          <t>144561</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183769</t>
+          <t>161192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>97872</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>77308</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>109007</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>73,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>83155</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>74341</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>90932</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>69,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>104738</t>
+          <t>83153</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81959</t>
+          <t>73891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118535</t>
+          <t>90663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>187893</t>
+          <t>181024</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163290</t>
+          <t>158206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204236</t>
+          <t>194223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>50371</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>39236</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>70935</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>47,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>36273</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>28496</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>45087</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>30,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>57879</t>
+          <t>35578</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44082</t>
+          <t>28068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80658</t>
+          <t>44840</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>94152</t>
+          <t>85950</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77809</t>
+          <t>72751</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>118755</t>
+          <t>108768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>48246</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>54791</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>60,33%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>80,24%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>47654</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>40517</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>54912</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>58,81%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>79,7%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49998</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42412</t>
+          <t>41528</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56704</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>97836</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86817</t>
+          <t>87659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106875</t>
+          <t>106971</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13496</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>39,67%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>21241</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13983</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28378</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>41,19%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22005</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29591</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>40808</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34023</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54081</t>
+          <t>50985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>416488</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>389189</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>439114</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>60,55%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>56,58%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>63,84%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>579</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>409433</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>383252</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>442254</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>58,32%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67,3%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>441693</t>
+          <t>385629</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>412248</t>
+          <t>364731</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>469504</t>
+          <t>405541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,27 +8125,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>851125</t>
+          <t>802117</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>813924</t>
+          <t>768300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>893701</t>
+          <t>832394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>271326</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>248700</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>298625</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>39,45%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>43,42%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>247720</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>214899</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>273901</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,68%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>305882</t>
+          <t>234998</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278071</t>
+          <t>215086</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>335327</t>
+          <t>255896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,22 +8238,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>553603</t>
+          <t>506324</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>511027</t>
+          <t>476047</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>590804</t>
+          <t>540141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>687814</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>747575</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1404728</t>
+          <t>1308441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
